--- a/docs/PRAP_Programming_Specification_v1.16.xlsx
+++ b/docs/PRAP_Programming_Specification_v1.16.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>PRAP_Development_Plan_v2.41.xlsx - APPROVED BASELINE, Dan 2026-08-02</t>
+          <t>PRAP_Development_Plan_v2.42.xlsx - APPROVED BASELINE, Dan 2026-08-02</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>Read directly from PRAP_Development_Plan_v2.41.xlsx sheet 03, so a requirement cannot be lost between the two documents.</t>
+          <t>Read directly from PRAP_Development_Plan_v2.42.xlsx sheet 03, so a requirement cannot be lost between the two documents.</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>The 'Monthly demand by project' pop-up now states THE MONTH'S TOTAL across every project in view, under a rule, and the band's share of it - the two things 'Monthly demand by person' already carried and this one did not. A band read on its own cannot say whether the month came to five FTE or to fifty. Sheet 10 Graph 1 updated. No change to any figure: the total is the sum the chart was already drawing, and it is the same figure Graph 2 states for that month summed along the other axis - test_charts.py now holds the two to agreeing in WORDS as well as in pixels, month for month.</t>
+          <t>The 'Monthly demand by project' pop-up now states THE MONTH'S TOTAL across every project in view, under a rule, and the band's share of it - the two things 'Monthly demand by person' already carried and this one did not. A band read on its own cannot say whether the month came to five FTE or to fifty. Sheet 10 Graph 1 updated. No change to any figure: the total is the sum the chart was already drawing, and it is the same figure Graph 2 states for that month summed along the other axis - test_charts.py now holds the two to agreeing in WORDS as well as in pixels, month for month. Written against plan v2.42.</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
@@ -3976,7 +3976,7 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>PRAP_Development_Plan_v2.41.xlsx</t>
+          <t>PRAP_Development_Plan_v2.42.xlsx</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
